--- a/DFA US/DFA.xlsx
+++ b/DFA US/DFA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/DFA US/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1660" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{144E7231-E45C-4703-9EAE-D81D3AA41DAB}"/>
+  <xr:revisionPtr revIDLastSave="1668" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A8C81A-6D9D-4699-85A3-BC50864D8B2B}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,10 +207,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -476,37 +472,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A50C80A-B9F0-42B2-B14F-324E5B39F7D5}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="34.42578125" customWidth="1"/>
+    <col min="3" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2022</v>
       </c>
       <c r="C3" s="1">
         <v>2023</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -516,32 +520,38 @@
       <c r="C4" s="5">
         <v>1824625</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="5">
         <v>3767</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="4">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <f>AVERAGE(C6:C6)</f>
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="F6" s="14"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -549,22 +559,28 @@
         <f>C5/C6</f>
         <v>1177187.5</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5">
         <v>124</v>
       </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -572,33 +588,39 @@
         <f>C9/C7</f>
         <v>1.0533581099017787E-4</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="4">
         <f>AVERAGE(C10:C10)</f>
         <v>1.0533581099017787E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="5">
         <v>25635</v>
       </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="5">
         <v>26</v>
       </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -606,9 +628,11 @@
         <f t="shared" ref="C14" si="0">C13/(C12+C13)</f>
         <v>1.0132107088577998E-3</v>
       </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -616,9 +640,11 @@
         <f>(C12+C13)/C7</f>
         <v>2.1798566498539951E-2</v>
       </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -626,16 +652,20 @@
         <f>C13/C7</f>
         <v>2.2086541014069551E-5</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="4">
         <f>AVERAGE(C16:C16)</f>
         <v>2.2086541014069551E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>7</v>
       </c>
@@ -643,20 +673,24 @@
       <c r="C18" s="13">
         <v>0.11</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13">
         <f>AVERAGE(C18:C18)</f>
         <v>0.11</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>13</v>
       </c>
@@ -665,38 +699,44 @@
         <f>C19/C7</f>
         <v>0</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4">
         <f>AVERAGE(C20:C20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="15">
         <v>2023</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>A10</f>
         <v>Lending income %</v>
@@ -706,12 +746,14 @@
         <f t="shared" ref="C25" si="1">C10</f>
         <v>1.0533581099017787E-4</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="9">
         <f>AVERAGE(C25:C25)</f>
         <v>1.0533581099017787E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>A20</f>
         <v>Brokerage commissions %</v>
@@ -721,15 +763,17 @@
         <f t="shared" ref="C26" si="2">C20</f>
         <v>0</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="9">
         <f>AVERAGE(C26:C26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>A15</f>
         <v>Dividend (gross)</v>
@@ -739,12 +783,14 @@
         <f t="shared" ref="C28" si="3">C15</f>
         <v>2.1798566498539951E-2</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="9">
         <f>AVERAGE(C28:C28)</f>
         <v>2.1798566498539951E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>A18</f>
         <v>Turnover</v>
@@ -754,68 +800,92 @@
         <f t="shared" ref="C29" si="4">C18</f>
         <v>0.11</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="16">
         <f>AVERAGE(C29:C29)</f>
         <v>0.11</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C30" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>C6-D10+D20</f>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4">
+        <f>C6-F10+F20</f>
         <v>3.0946641890098221E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="8"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C34" s="4"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="10"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="10"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="10"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="10"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="10"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="10"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -825,37 +895,45 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9939E4F9-461F-4568-B5ED-8086F133870D}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="34.42578125" customWidth="1"/>
+    <col min="3" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="7"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>2022</v>
       </c>
       <c r="C3" s="1">
         <v>2023</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -865,32 +943,38 @@
       <c r="C4" s="5">
         <v>1281622</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="5">
         <v>3872</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="4">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <f>AVERAGE(C6:C6)</f>
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="F6" s="14"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -898,22 +982,28 @@
         <f>C5/C6</f>
         <v>921904.76190476201</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5">
         <v>344</v>
       </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -921,33 +1011,39 @@
         <f>C9/C7</f>
         <v>3.7314049586776855E-4</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="4">
         <f>AVERAGE(C10:C10)</f>
         <v>3.7314049586776855E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="5">
         <v>37428</v>
       </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="5">
         <v>4990</v>
       </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -955,9 +1051,11 @@
         <f t="shared" ref="C14" si="0">C13/(C12+C13)</f>
         <v>0.11763873827148852</v>
       </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -965,9 +1063,11 @@
         <f>(C12+C13)/C7</f>
         <v>4.6011260330578507E-2</v>
       </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -975,16 +1075,20 @@
         <f>C13/C7</f>
         <v>5.4127066115702473E-3</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="4">
         <f>AVERAGE(C16:C16)</f>
         <v>5.4127066115702473E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C17" s="9"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>7</v>
       </c>
@@ -992,20 +1096,24 @@
       <c r="C18" s="13">
         <v>0.13</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13">
         <f>AVERAGE(C18:C18)</f>
         <v>0.13</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>13</v>
       </c>
@@ -1014,38 +1122,44 @@
         <f>C19/C7</f>
         <v>0</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4">
         <f>AVERAGE(C20:C20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="15">
         <v>2023</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>A10</f>
         <v>Lending income %</v>
@@ -1055,12 +1169,14 @@
         <f t="shared" ref="C25" si="1">C10</f>
         <v>3.7314049586776855E-4</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="9">
         <f>AVERAGE(C25:C25)</f>
         <v>3.7314049586776855E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>A20</f>
         <v>Brokerage commissions %</v>
@@ -1070,15 +1186,17 @@
         <f t="shared" ref="C26" si="2">C20</f>
         <v>0</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="9">
         <f>AVERAGE(C26:C26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>A15</f>
         <v>Dividend (gross)</v>
@@ -1088,12 +1206,14 @@
         <f t="shared" ref="C28" si="3">C15</f>
         <v>4.6011260330578507E-2</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="9">
         <f>AVERAGE(C28:C28)</f>
         <v>4.6011260330578507E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>A18</f>
         <v>Turnover</v>
@@ -1103,68 +1223,92 @@
         <f t="shared" ref="C29" si="4">C18</f>
         <v>0.13</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="16">
         <f>AVERAGE(C29:C29)</f>
         <v>0.13</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C30" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="4">
-        <f>C6-D10+D20</f>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4">
+        <f>C6-F10+F20</f>
         <v>3.8268595041322313E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="8"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C34" s="4"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="10"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="10"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="11"/>
       <c r="C39" s="10"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="11"/>
       <c r="C40" s="10"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="10"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="10"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
